--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13279,17 +13279,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13311,17 +13311,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13530,22 +13530,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13754,22 +13754,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -13818,22 +13818,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14148,12 +14148,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14362,22 +14362,22 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14874,22 +14874,22 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15460,12 +15460,12 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15610,22 +15610,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15674,22 +15674,22 @@
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15834,22 +15834,22 @@
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15962,22 +15962,22 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16122,22 +16122,22 @@
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16154,22 +16154,22 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16186,22 +16186,22 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16228,12 +16228,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16452,12 +16452,12 @@
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16634,7 +16634,7 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -16644,12 +16644,12 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17348,12 +17348,12 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17375,17 +17375,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17498,22 +17498,22 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18042,22 +18042,22 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18106,22 +18106,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,29 +18259,29 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18330,22 +18330,22 @@
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18431,17 +18431,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18463,17 +18463,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
@@ -13279,17 +13279,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -13530,22 +13530,22 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13914,22 +13914,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13946,22 +13946,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14596,12 +14596,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14618,22 +14618,22 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15482,7 +15482,7 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15898,7 +15898,7 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15940,12 +15940,12 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15962,22 +15962,22 @@
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16154,22 +16154,22 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16186,22 +16186,22 @@
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16314,22 +16314,22 @@
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16612,12 +16612,12 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16794,22 +16794,22 @@
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16890,22 +16890,22 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17375,17 +17375,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17444,12 +17444,12 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17818,22 +17818,22 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18042,22 +18042,22 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18106,22 +18106,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18148,12 +18148,12 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18323,29 +18323,29 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,29 +18419,29 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13279,17 +13279,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13759,17 +13759,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13914,22 +13914,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13946,7 +13946,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -13956,12 +13956,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15162,22 +15162,22 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15354,22 +15354,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15482,22 +15482,22 @@
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15898,22 +15898,22 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16228,12 +16228,12 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17316,12 +17316,12 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17375,17 +17375,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17594,7 +17594,7 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
@@ -17604,12 +17604,12 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17658,22 +17658,22 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17818,22 +17818,22 @@
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18106,22 +18106,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18148,12 +18148,12 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,29 +18419,29 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18463,17 +18463,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,29 +18547,29 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13535,17 +13535,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13690,22 +13690,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
@@ -13727,17 +13727,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
@@ -13818,22 +13818,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13882,22 +13882,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13978,22 +13978,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15354,22 +15354,22 @@
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15386,22 +15386,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15428,12 +15428,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15546,22 +15546,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16154,22 +16154,22 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16890,7 +16890,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -16900,12 +16900,12 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16932,12 +16932,12 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17380,12 +17380,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17594,22 +17594,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17626,22 +17626,22 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17658,22 +17658,22 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17732,12 +17732,12 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17828,12 +17828,12 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17892,12 +17892,12 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18106,22 +18106,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18148,12 +18148,12 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18170,22 +18170,22 @@
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18195,29 +18195,29 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,29 +18419,29 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18463,17 +18463,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18554,22 +18554,22 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
@@ -13311,17 +13311,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
@@ -13594,22 +13594,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13818,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -13828,12 +13828,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13882,22 +13882,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13978,22 +13978,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14042,22 +14042,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14394,22 +14394,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14564,12 +14564,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15194,22 +15194,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15386,22 +15386,22 @@
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15546,22 +15546,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16154,22 +16154,22 @@
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16388,12 +16388,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16922,22 +16922,22 @@
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16964,12 +16964,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17380,12 +17380,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17626,22 +17626,22 @@
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17786,22 +17786,22 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18052,12 +18052,12 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18138,22 +18138,22 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18163,29 +18163,29 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,29 +18419,29 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,29 +18451,29 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -13151,17 +13151,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13503,17 +13503,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13663,17 +13663,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13695,17 +13695,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,7 +13747,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -13860,12 +13860,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13978,22 +13978,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14042,22 +14042,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14266,22 +14266,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14394,22 +14394,22 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14426,22 +14426,22 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14724,12 +14724,12 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15172,12 +15172,12 @@
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15194,22 +15194,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15290,22 +15290,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15428,12 +15428,12 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15610,22 +15610,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16100,12 +16100,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16415,17 +16415,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16698,22 +16698,22 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16730,22 +16730,22 @@
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17375,17 +17375,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17498,22 +17498,22 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17786,22 +17786,22 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18052,12 +18052,12 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18180,12 +18180,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18212,12 +18212,12 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18234,22 +18234,22 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18458,22 +18458,22 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,7 +12856,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13146,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,29 +13619,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13818,22 +13818,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14276,12 +14276,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14682,22 +14682,22 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14756,12 +14756,12 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14906,22 +14906,22 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14970,22 +14970,22 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15290,22 +15290,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15610,22 +15610,22 @@
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16132,12 +16132,12 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16218,22 +16218,22 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16516,12 +16516,12 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16612,12 +16612,12 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17375,17 +17375,17 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17434,22 +17434,22 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17498,22 +17498,22 @@
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17892,12 +17892,12 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17946,22 +17946,22 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18042,22 +18042,22 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18234,22 +18234,22 @@
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18431,17 +18431,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18463,17 +18463,17 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18532,12 +18532,12 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,29 +18547,29 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市江津区爱情海购物广场</t>
+          <t>小米汽车重庆市永川区永川万达</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>重庆市江津区爱情海购物广场L1层中庭</t>
+          <t>中国重庆市永川区星光大道789号永川万达</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车重庆市永川区永川万达</t>
+          <t>小米汽车重庆市江津区爱情海购物广场</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>中国重庆市永川区星光大道789号永川万达</t>
+          <t>重庆市江津区爱情海购物广场L1层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
@@ -13407,17 +13407,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
@@ -13658,22 +13658,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
@@ -13695,17 +13695,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
@@ -13818,22 +13818,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14148,12 +14148,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14490,7 +14490,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -14500,12 +14500,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15460,12 +15460,12 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15642,22 +15642,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16036,12 +16036,12 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16090,22 +16090,22 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16218,22 +16218,22 @@
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16250,22 +16250,22 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16676,12 +16676,12 @@
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17178,22 +17178,22 @@
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17242,22 +17242,22 @@
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17658,22 +17658,22 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17946,22 +17946,22 @@
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18042,22 +18042,22 @@
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18074,22 +18074,22 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18372,12 +18372,12 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18458,22 +18458,22 @@
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,29 +18547,29 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12137,7 +12137,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-罗湖卫星展厅</t>
+          <t>深圳中升悦晟-福田电气化体验馆</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
+          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>深圳中升悦晟-福田电气化体验馆</t>
+          <t>深圳中升悦晟-罗湖卫星展厅</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>深圳市福田区福田街道岗厦社区深南大道2001号嘉麟豪庭102</t>
+          <t>深圳市罗湖区清水河三路博丰大厦一层</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
@@ -13343,17 +13343,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
@@ -13375,17 +13375,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,7 +13395,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
@@ -13407,17 +13407,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13882,22 +13882,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13946,22 +13946,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14015,17 +14015,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14106,22 +14106,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14490,22 +14490,22 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14692,12 +14692,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14714,22 +14714,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14751,17 +14751,17 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14815,17 +14815,17 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14842,22 +14842,22 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15108,12 +15108,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15199,17 +15199,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15546,22 +15546,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15642,22 +15642,22 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15802,22 +15802,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15866,22 +15866,22 @@
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15898,22 +15898,22 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15999,17 +15999,17 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16090,22 +16090,22 @@
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16410,22 +16410,22 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16831,17 +16831,17 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17050,22 +17050,22 @@
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17092,12 +17092,12 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17151,17 +17151,17 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17444,12 +17444,12 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17476,12 +17476,12 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17594,22 +17594,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17658,22 +17658,22 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18074,22 +18074,22 @@
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18138,22 +18138,22 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18180,12 +18180,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18202,22 +18202,22 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18399,17 +18399,17 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18431,17 +18431,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,29 +18451,29 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,29 +18515,29 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京市大兴区大兴龙湖天街</t>
+          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>北京市大兴区大兴龙湖天街一层中庭</t>
+          <t>双林东路8号万开基地二期B座</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区西四环双林东路服务中心</t>
+          <t>小米汽车北京市大兴区大兴龙湖天街</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>双林东路8号万开基地二期B座</t>
+          <t>北京市大兴区大兴龙湖天街一层中庭</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南西城龙湖天街广场</t>
+          <t>蔚来空间 | 济南世纪大道万达广场</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
+          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 济南世纪大道万达广场</t>
+          <t>蔚来空间 | 济南西城龙湖天街广场</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5099号鲁商凤凰广场二期商业楼349号济南世纪大道万达广场LG层-1030号铺位</t>
+          <t>山东省济南市槐荫区经十路29299号 (经十路与腊山河东路交叉口)西城龙湖天街A-1F-04</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海零售中心</t>
+          <t>理想汽车江门江海服务中心（利生车城店）</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>江门市江海区银帆路2号5幢-2</t>
+          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>理想汽车江门江海服务中心（利生车城店）</t>
+          <t>理想汽车江门江海零售中心</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>广东省江门市江海区银帆路2号5幢(利生车城)</t>
+          <t>江门市江海区银帆路2号5幢-2</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛凯德Mall</t>
+          <t>华为智能生活馆•青岛乐客城</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
+          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•青岛乐客城</t>
+          <t>华为智能生活馆•青岛凯德Mall</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>山东省青岛市李沧区夏庄路1号伟东乐客城1F+2F华为智能生活馆</t>
+          <t>山东省青岛市市北区黑龙江南路凯德MALL1层11A/11B号</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,29 +13459,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,14 +13491,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,29 +13555,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,14 +13619,14 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -13636,12 +13636,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13850,22 +13850,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13882,22 +13882,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13924,12 +13924,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13946,22 +13946,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14020,12 +14020,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14911,17 +14911,17 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15007,17 +15007,17 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15108,12 +15108,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15194,22 +15194,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15263,17 +15263,17 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15290,22 +15290,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15492,12 +15492,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15546,22 +15546,22 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省揭阳揭东区揭东大道服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15743,17 +15743,17 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15807,17 +15807,17 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15898,22 +15898,22 @@
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15994,22 +15994,22 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16100,12 +16100,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16255,17 +16255,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16282,22 +16282,22 @@
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16324,12 +16324,12 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省衡阳市蒸湘区杨柳汽贸城服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16383,17 +16383,17 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16420,12 +16420,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16479,17 +16479,17 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16602,22 +16602,22 @@
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16639,17 +16639,17 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16868,12 +16868,12 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17087,17 +17087,17 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17114,22 +17114,22 @@
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17215,17 +17215,17 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17279,17 +17279,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17370,22 +17370,22 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17567,17 +17567,17 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17594,22 +17594,22 @@
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17636,12 +17636,12 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17887,17 +17887,17 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17924,12 +17924,12 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18111,17 +18111,17 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18138,22 +18138,22 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18163,7 +18163,7 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18180,12 +18180,12 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18202,22 +18202,22 @@
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18227,7 +18227,7 @@
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18323,7 +18323,7 @@
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,29 +18387,29 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>潍坊易豪4S中心</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>潍坊鑫易豪4S中心</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 89%</t>
         </is>
       </c>
     </row>
@@ -18431,17 +18431,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,29 +18515,29 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>潍坊易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>潍坊鑫易豪4S中心</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 89%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260518_vs_20260525.xlsx
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春华润万象城零售中心</t>
+          <t>理想汽车长春中东新天地零售中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
+          <t>吉林省长春市南关区亚泰大街1138号</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>理想汽车长春中东新天地零售中心</t>
+          <t>理想汽车长春华润万象城零售中心</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>吉林省长春市南关区亚泰大街1138号</t>
+          <t>吉林省长春市南关区人民大街3388号长春万象城L236号商铺</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
+          <t>理想汽车潍坊青州汽车园零售展厅</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -10754,7 +10754,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
+          <t>青州市玲珑山北路2359号</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>理想汽车潍坊青州汽车园零售展厅</t>
+          <t>理想汽车潍坊寿光授权钣喷中心（广宝店）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>青州市玲珑山北路2359号</t>
+          <t>山东省潍坊市寿光市文家街道圣城西街666号</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京龙湖长楹天街</t>
+          <t>鸿蒙智行智界用户中心•北京房山城关</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
+          <t>北京市房山区城关街道顾八路一区2号</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•北京房山城关</t>
+          <t>华为智能生活馆•北京龙湖长楹天街</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>北京市房山区城关街道顾八路一区2号</t>
+          <t>北京市朝阳区常通路1号院龙湖长楹天街东区一层B栋-2F-C32，B栋-1F-19a，B栋-2F-21，B栋-1F-19b，B栋-2F-19a，B栋-2F-19b，B栋-2F-20号商铺</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
+          <t>理想汽车衢州吾悦广场零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>衢州市衢江区振兴东路599号</t>
+          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>理想汽车衢州吾悦广场零售中心</t>
+          <t>理想汽车衢州衢江服务中心（振兴东路店）</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>浙江省衢州市柯城区白云中大道路99号吾悦广场1019-1商铺理想汽车</t>
+          <t>衢州市衢江区振兴东路599号</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「理想汽车常州钟楼吾悦广场零售中心」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（长楹龙湖）</t>
+          <t>华为智能生活馆•北京颐堤港</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
+          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>华为智能生活馆•北京颐堤港</t>
+          <t>华为授权体验店（长楹龙湖）</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>北京市朝阳区酒仙桥路18号颐堤港商场一层</t>
+          <t>北京市朝阳区常通镇常通路龙湖长楹天街F1+F2</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（星河COCOCity）</t>
+          <t>华为授权体验店（西田城）</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
+          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（西田城）</t>
+          <t>华为授权体验店（南湖天地）</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市联合路97号西田城1楼10-11号</t>
+          <t>浙江省嘉兴市南湖区南湖街道171号</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期</t>
+          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>华为授权体验店（南湖天地）</t>
+          <t>华为授权体验店（星河COCOCity）</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区南湖街道171号</t>
+          <t>浙江省嘉兴市南湖区长水路1810号星河COCOCity</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>连续在档 3 期；本期存在高相似店名「华为授权体验店（济南新辰天地）」（疑似改名/合并，非真实关店）</t>
+          <t>连续在档 3 期</t>
         </is>
       </c>
     </row>
@@ -13146,22 +13146,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
+          <t>宁波众国融之宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13171,29 +13171,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
+          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>宝马</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
+          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13203,29 +13203,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
+          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（王府井购物中心）</t>
+          <t>理想汽车深圳南山服务中心（嘉进隆汽车城店）</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13235,29 +13235,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
+          <t>深圳市南山区南头街道嘉进隆前海汽车城B03栋4楼 → 深圳市南山区南头街道嘉进隆前海汽车城B03栋1楼</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上海益申汽车销售服务有限公司</t>
+          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13267,29 +13267,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
+          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家北京市顺义区祥云小镇汽车体验店</t>
+          <t>小鹏汽车佛山顺德销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13299,29 +13299,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安泰大街9号祥云小镇购物中心南区【10-102/103/111】号商铺 → 安泰大街6号院10号楼1层102号、103号</t>
+          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
+          <t>郑州中升沃茂4S中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
+          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐众国融宝汽车销售服务有限公司</t>
+          <t>理想汽车鄂尔多斯市康巴什零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13363,29 +13363,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>新疆乌鲁木齐市米东区永顺街1599号新疆骏豪汽车销售服务有限公司上海荣威4S店5栋4S店101室 → 新疆乌鲁木齐市米东区永顺街1599号</t>
+          <t>鄂尔多斯市康巴什区鄂尔多斯市康巴什区永宁街1号 → 鄂尔多斯市康巴什区碳中和研究院理想汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车锦州太和零售展厅</t>
+          <t>小米汽车安徽合肥居巢区巢湖万达</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13395,29 +13395,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
+          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>郑州中升沃茂4S中心</t>
+          <t>理想汽车锦州太和零售展厅</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13427,29 +13427,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内27号 → 河南省郑州市惠济区花园路与开元路交叉口向南50米河南省汽贸中心院内</t>
+          <t>辽宁省锦州市太和区南广路102号 → 辽宁省锦州市太和区南广路101-2号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F → 东塘路80号合肥巢湖万达广场1F</t>
+          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
         </is>
       </c>
     </row>
@@ -13471,17 +13471,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宁波天一广场销售中心</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13491,29 +13491,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
+          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宝马</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宁波众国融之宝汽车销售服务有限公司</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13523,29 +13523,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>浙江省宁波市江北区环城北路东段83号 → 浙江省宁波市江北区环城北路东段83号11幢1层</t>
+          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>理想汽车滨州滨城服务中心（渤海二十四路店）</t>
+          <t>上海益申汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>滨城区渤海二十四路501号 → 山东省滨州市滨城区渤海二十四路与长江一路交叉口往北250米路西</t>
+          <t>上海市青浦区华新镇华腾路1328、1358、1386、1388号3幢 → 上海市青浦区香花桥街道北青公路9595号</t>
         </is>
       </c>
     </row>
@@ -13567,17 +13567,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车宁波天一广场销售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13587,29 +13587,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南道南50米路东 → 河北省廊坊市霸州市106国道王伍房南路东</t>
+          <t>浙江省宁波市海曙区日新街88号 → 浙江省宁波市海曙区天一广场药行街 88 号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>北京中升</t>
+          <t>小鹏汽车贵阳林城西路销售展厅</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
+          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
         </is>
       </c>
     </row>
@@ -13631,17 +13631,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车佛山顺德销售服务中心</t>
+          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13651,29 +13651,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>佛山市顺德区大良街道新松社区105国道新松路段6号 → 广东省佛山市顺德区大良街道横八路21号(小鹏汽车佛山顺德交付中心)</t>
+          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>武汉中升</t>
+          <t>华为授权体验店（王府井购物中心）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13683,29 +13683,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
+          <t>江西省南昌市青云谱区洪城路158号王府井购物中心G-1F-P021、G-1F-P022A → 江西省南昌市青云谱区洪城路158号王府井购物中心G-2F-P021</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>北京中升</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13715,29 +13715,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>周口市大庆路与太清路交叉口向东50米路北门四跨店面 16号 → 河南省周口市川汇区太清路万国车世界一楼</t>
+          <t>北京市朝阳区五元桥向北3公里 → 北京市朝阳区香江北路临甲1号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宜兴融达汽车城销售服务中心</t>
+          <t>西安丽骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13747,29 +13747,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>宜兴市经济开发区融达汽车城西氿大道90号 → 无锡市宜兴市经济开发区融达汽车城西氿大道90号</t>
+          <t>锦业一路与丈八二路交叉口东南角永威时代中心一楼西侧 永威时代中心 Xi'an High-tech Zone → 锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>雷克萨斯</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车贵阳林城西路销售展厅</t>
+          <t>武汉中升</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市观山湖区林城西路248号通源汽车文化广场内 → 贵州省贵阳市观山湖区金阳街道林城西路248号通源汽车文化广场内</t>
+          <t>湖北省武汉市洪山区青菱乡华中动力产业园内二期一号 → 武汉市黄陂区盘龙城经济开发区许庙村巨龙大道222号盘龙汽车城</t>
         </is>
       </c>
     </row>
@@ -13823,17 +13823,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
+          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13855,17 +13855,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
+          <t>小米汽车广东河源市源城区河源大道服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13887,17 +13887,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
+          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13919,17 +13919,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街授权服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉市东西湖区东西湖团结街服务中心</t>
+          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13951,17 +13951,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
+          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13983,17 +13983,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
+          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -14047,17 +14047,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
+          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -14079,17 +14079,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
+          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -14111,17 +14111,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
+          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
+          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -14175,17 +14175,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
+          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14207,17 +14207,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
+          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省成都温江区新华大道服务中心</t>
+          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14271,17 +14271,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
+          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14303,17 +14303,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
+          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路授权服务中心</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
+          <t>小米汽车浙江省舟山普陀区新惠路服务中心</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -14367,17 +14367,17 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
+          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -14399,17 +14399,17 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
+          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -14431,17 +14431,17 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
+          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -14463,17 +14463,17 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
+          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14495,17 +14495,17 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
+          <t>小米汽车北京市南四环中路临时授权服务中心</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
+          <t>小米汽车北京市南四环中路临时服务中心</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
+          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -14559,17 +14559,17 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
+          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
+          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道授权服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东河源市源城区河源大道服务中心</t>
+          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14655,17 +14655,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海市嘉定区星华公路服务中心</t>
+          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14687,17 +14687,17 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
+          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14719,17 +14719,17 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道授权服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥市蜀山区方兴大道服务中心</t>
+          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14746,22 +14746,22 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵州电动</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•广西电动</t>
+          <t>小米汽车河南省商丘市梁园区传驰汽车园服务中心</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
+          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14810,22 +14810,22 @@
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•南网电动</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•海南电动</t>
+          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14847,17 +14847,17 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路授权服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南焦作市解放区迎宾路服务中心</t>
+          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14879,17 +14879,17 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道授权服务中心</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
+          <t>小米汽车广东省深圳市龙岗区坂田街道服务中心</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -14943,17 +14943,17 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
+          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -14975,17 +14975,17 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路授权服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南省大理市晨光路服务中心</t>
+          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -15002,22 +15002,22 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
+          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
+          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -15039,17 +15039,17 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路授权服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省乐山市高新区龙安路服务中心</t>
+          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
+          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -15103,17 +15103,17 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
+          <t>小米汽车云南省大理市晨光路授权服务中心</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
+          <t>小米汽车云南省大理市晨光路服务中心</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
+          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -15167,17 +15167,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖授权服务中心</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
+          <t>小米汽车广东省东莞市松山湖区松山湖服务中心</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -15194,22 +15194,22 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
+          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
+          <t>小米汽车山东东营市经开区府前大街服务中心</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -15231,17 +15231,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路授权服务中心</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
+          <t>小米汽车湖南省岳阳市经济技术开发区巴陵东路服务中心</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
+          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -15290,22 +15290,22 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中信恒业</t>
+          <t>AITO授权用户中心•南网电动</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>牡丹江中源恒业</t>
+          <t>AITO授权用户中心•海南电动</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -15327,17 +15327,17 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
+          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -15359,17 +15359,17 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>小米汽车三明市三元区三明汽车城服务中心</t>
+          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -15391,17 +15391,17 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达授权服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省廊坊市广阳区众奥达服务中心</t>
+          <t>小米汽车贵州省遵义市新蒲新区嘉汇汽车广场服务中心</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -15423,17 +15423,17 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区国际汽车城授权服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道授权服务中心</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省泰州市海陵区泰州大道服务中心</t>
+          <t>小米汽车河南省周口市川汇区周口大道服务中心</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -15455,17 +15455,17 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道授权服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省宜春市袁州区武功山大道服务中心</t>
+          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -15487,17 +15487,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
+          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -15519,17 +15519,17 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富授权服务中心</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
+          <t>小米汽车广东省湛江市麻章区金富服务中心</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -15551,17 +15551,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
+          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -15583,17 +15583,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
+          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -15615,17 +15615,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城授权服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省常德市武陵区湘西北汽车城服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -15647,17 +15647,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路授权服务中心</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
+          <t>小米汽车云南昭通市昭阳区龙泉路服务中心</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路授权服务中心</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
+          <t>小米汽车河北省沧州市运河区向海路服务中心</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -15711,17 +15711,17 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
+          <t>小米汽车四川省西昌市攀西汽车城服务中心</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -15738,22 +15738,22 @@
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
+          <t>华为授权体验店（爱车小镇）</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
+          <t>华为授权体验店（海八路爱车小镇）</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -15775,17 +15775,17 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
+          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -15802,22 +15802,22 @@
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
+          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -15839,17 +15839,17 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路授权服务中心</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
+          <t>小米汽车河北张家口市经济开发区胜利南路服务中心</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -15871,17 +15871,17 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
+          <t>小米汽车三明市三元区三明汽车城服务中心</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城授权服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道授权服务中心</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>小米汽车商丘市永城市春雨汽车城服务中心</t>
+          <t>小米汽车湖北十堰市茅箭区东风大道服务中心</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -15935,17 +15935,17 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站授权服务中心</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
+          <t>小米汽车山西省长治市开发区高铁东站服务中心</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -15967,17 +15967,17 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路授权服务中心</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
+          <t>小米汽车浙江杭州余杭区嘉企路服务中心</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -15994,22 +15994,22 @@
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>南昌红谷滩保时捷中心</t>
+          <t>小米汽车陕西省西安市未央区西三环授权服务中心</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>南昌保时捷中心</t>
+          <t>小米汽车陕西省西安市未央区西三环服务中心</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -16031,17 +16031,17 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道授权服务中心</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
+          <t>小米汽车河南省驻马店市驿城区中原大道服务中心</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
+          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
+          <t>小米汽车广东广州花都区建设北路服务中心</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -16095,17 +16095,17 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>小米汽车莆田市荔城区奇奇服务中心</t>
+          <t>小米汽车安徽省阜阳市经济技术开发区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -16127,17 +16127,17 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路授权服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路授权服务中心</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东聊城市东昌府区光岳路服务中心</t>
+          <t>小米汽车福建省福州市仓山区高旺路服务中心</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -16159,17 +16159,17 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道授权服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道授权服务中心</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>小米汽车玉林市玉州区玉北大道服务中心</t>
+          <t>小米汽车湖北省荆州市荆州区荆沙大道服务中心</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -16191,17 +16191,17 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城授权服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道授权服务中心</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省盐城市盐都区永宁汽车城服务中心</t>
+          <t>小米汽车安徽宿州市埇桥区金海大道服务中心</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -16223,17 +16223,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城授权服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省许昌市魏都区魏都汽贸城服务中心</t>
+          <t>小米汽车铜仁市碧江区灯塔汽车城服务中心</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -16260,12 +16260,12 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城授权服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路授权服务中心</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江丽水市莲都区岩泉汽车城服务中心</t>
+          <t>小米汽车浙江省温州市乐清市宁康东路服务中心</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -16287,17 +16287,17 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街授权服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东东营市经开区府前大街服务中心</t>
+          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -16319,17 +16319,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
+          <t>小米汽车新疆阿克苏市温宿县大欣汽车城服务中心</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路授权服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路授权服务中心</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省镇江市润州区官塘桥路服务中心</t>
+          <t>小米汽车广西柳州市鱼峰区西江路服务中心</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -16378,22 +16378,22 @@
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道授权服务中心</t>
+          <t>理想汽车伊犁巴彦岱临时交付中心</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省信阳市高新区南京大道服务中心</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -16410,7 +16410,7 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -16420,12 +16420,12 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心店</t>
+          <t>小米汽车广东省珠海市香洲区三溪路授权服务中心</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>理想汽车南山嘉进隆零售中心</t>
+          <t>小米汽车广东省珠海市香洲区三溪路服务中心</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城授权服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建省泉州市洛江区信兴汽车城服务中心</t>
+          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -16474,22 +16474,22 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
+          <t>牡丹江中信恒业</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
+          <t>牡丹江中源恒业</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -16511,17 +16511,17 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城授权服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省连云港市海州区振兴汽车城服务中心</t>
+          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -16543,17 +16543,17 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路授权服务中心</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
+          <t>小米汽车安徽省六安市金安区凤凰路服务中心</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -16575,17 +16575,17 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道授权服务中心</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
+          <t>小米汽车四川省成都温江区新华大道服务中心</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -16607,17 +16607,17 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
+          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -16634,22 +16634,22 @@
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场授权服务中心</t>
+          <t>理想汽车溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区润华汽车广场服务中心</t>
+          <t>理想汽车常州溧阳上河城零售中心</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -16671,17 +16671,17 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城授权服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道授权服务中心</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡市江阴市夏港国际汽车城服务中心</t>
+          <t>小米汽车河南省新乡市牧野区新中大道服务中心</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -16703,17 +16703,17 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道授权服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街授权服务中心</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省上饶市信州区上饶大道服务中心</t>
+          <t>小米汽车辽宁省沈阳市皇姑区鸭绿江街服务中心</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路授权服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省清远市清城区建设二路服务中心</t>
+          <t>小米汽车四川省宜宾市叙州区德福汽车城服务中心</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -16767,17 +16767,17 @@
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城授权服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北恩施市花果山汽贸城服务中心</t>
+          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -16799,17 +16799,17 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路授权服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路授权服务中心</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省阳江市阳东区广雅东路服务中心</t>
+          <t>小米汽车运城市盐湖区学苑北路服务中心</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -16826,22 +16826,22 @@
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁巴彦岱临时交付中心</t>
+          <t>小米汽车广东省江门市江海区利生车城授权服务中心</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
+          <t>小米汽车广东省江门市江海区利生车城服务中心</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -16863,17 +16863,17 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
+          <t>小米汽车湖南省怀化市鹤城区国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -16895,17 +16895,17 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城授权服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省无锡宜兴市国际汽车城服务中心</t>
+          <t>小米汽车安徽省蚌埠市禹会区蚌埠国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城授权服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道授权服务中心</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省安庆市宜秀区英德利汽车城服务中心</t>
+          <t>小米汽车四川省眉山东坡区眉州大道服务中心</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -16959,17 +16959,17 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时授权服务中心</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
+          <t>小米汽车新疆乌鲁木齐市水磨沟区南湖北路临时服务中心</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -16991,17 +16991,17 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路授权服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路授权服务中心</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省郴州市北湖区国庆南路服务中心</t>
+          <t>小米汽车山东滨州市滨城区北外环路服务中心</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -17018,22 +17018,22 @@
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>理想汽车溧阳上河城零售中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>理想汽车常州溧阳上河城零售中心</t>
+          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -17055,17 +17055,17 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街授权服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道授权服务中心</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>小米汽车赤峰市喀喇沁旗临潢大街服务中心</t>
+          <t>小米汽车云南曲靖市麒麟区珠江源大道服务中心</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
@@ -17082,22 +17082,22 @@
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道授权服务中心</t>
+          <t>理想汽车湛江赤坎服务中心（椹川大道店）</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川成都市双流区双楠大道服务中心</t>
+          <t>理想汽车湛江赤坎瀚龙车城零售中心</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -17119,17 +17119,17 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道授权服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道授权服务中心</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东韶关市浈江区浈江大道服务中心</t>
+          <t>小米汽车湖南省长沙市岳麓区岳麓大道服务中心</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -17146,7 +17146,7 @@
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（爱车小镇）</t>
+          <t>理想汽车南山嘉进隆零售中心店</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（海八路爱车小镇）</t>
+          <t>理想汽车南山嘉进隆零售中心</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
@@ -17183,17 +17183,17 @@
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路授权服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路授权服务中心</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖南省株洲市天元区湘山路服务中心</t>
+          <t>小米汽车江苏省淮安市淮阴区香港路服务中心</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -17210,22 +17210,22 @@
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
+          <t>理想汽车临汾尧都授权钣喷中心（友邻店）</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
+          <t>理想汽车临汾尧都秦蜀路临时交付中心店</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -17247,17 +17247,17 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路授权服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路授权服务中心</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省黄冈市黄州区南湖路服务中心</t>
+          <t>小米汽车上海市嘉定区星华公路服务中心</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -17274,22 +17274,22 @@
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路授权服务中心</t>
+          <t>南昌红谷滩保时捷中心</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽宣城市宣州区柏枧山路服务中心</t>
+          <t>南昌保时捷中心</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -17311,17 +17311,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路授权服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路授权服务中心</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区建设北路服务中心</t>
+          <t>小米汽车四川省绵阳市涪城区绵兴中路服务中心</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -17343,17 +17343,17 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
+          <t>小米汽车宁夏银川兴庆区金三角国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
@@ -17370,7 +17370,7 @@
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
@@ -17380,12 +17380,12 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权钣喷中心（鑫想店）</t>
+          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>理想汽车衢州衢江授权服务中心（鑫想店）</t>
+          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
@@ -17407,17 +17407,17 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路授权服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇授权服务中心</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河南省开封市龙亭区魏都路服务中心</t>
+          <t>小米汽车湖州市吴兴区织里镇服务中心</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -17439,17 +17439,17 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时授权服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道授权服务中心</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>小米汽车北京市南四环中路临时服务中心</t>
+          <t>小米汽车安徽省亳州市经济开发区药都大道服务中心</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
@@ -17471,17 +17471,17 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道授权服务中心</t>
+          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省孝感市孝南区孝武大道服务中心</t>
+          <t>小米汽车达州市高新区金龙大道服务中心</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
@@ -17503,17 +17503,17 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城授权服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>小米汽车咸阳市秦都区南上召汽车城服务中心</t>
+          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
@@ -17535,17 +17535,17 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园授权服务中心</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
+          <t>小米汽车安徽马鞍山市雨山区佳达汽车园服务中心</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
@@ -17572,12 +17572,12 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路授权服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道授权服务中心</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省九江市濂溪区九湖路服务中心</t>
+          <t>小米汽车吉安市吉州区吉兴大道服务中心</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
@@ -17599,17 +17599,17 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道授权服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路授权服务中心</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>小米汽车达州市高新区金龙大道服务中心</t>
+          <t>小米汽车宝鸡市渭滨区高新十二路服务中心</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
@@ -17631,17 +17631,17 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇授权服务中心</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
+          <t>小米汽车莆田市荔城区奇奇服务中心</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -17663,17 +17663,17 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城授权服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道授权服务中心</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北邢台市任泽区东部车城服务中心</t>
+          <t>小米汽车山东德州市经济开发区晶华大道服务中心</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -17695,17 +17695,17 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站授权服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道授权服务中心</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳市观山湖区贵阳高铁北站服务中心</t>
+          <t>小米汽车湖北省仙桃市国家高新区东城大道服务中心</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -17727,17 +17727,17 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路授权服务中心</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
+          <t>小米汽车河南濮阳市经开区中原路服务中心</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -17759,17 +17759,17 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市授权服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道授权服务中心</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>小米汽车云南昆明市经开区金菱车市服务中心</t>
+          <t>小米汽车湖北省黄石市下陆区发展大道服务中心</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
@@ -17791,17 +17791,17 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路授权服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路授权服务中心</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东泰安市岱岳区长城路服务中心</t>
+          <t>小米汽车山西省太原市小店区太榆路服务中心</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -17823,17 +17823,17 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路授权服务中心</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路服务中心</t>
+          <t>小米汽车山东省菏泽市牡丹区人民南路服务中心</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -17855,17 +17855,17 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路授权服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路授权服务中心</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>小米汽车秦皇岛市海港区北环路服务中心</t>
+          <t>小米汽车河南省南阳市高新区信臣西路服务中心</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -17892,12 +17892,12 @@
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道授权服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路授权服务中心</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江温州市苍南县苍南大道服务中心</t>
+          <t>小米汽车浙江省绍兴诸暨市千禧路服务中心</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -17919,17 +17919,17 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城授权服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省惠州市惠城区汝湖汽车城服务中心</t>
+          <t>小米汽车海南省三亚市吉阳区诚越汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -17951,17 +17951,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路授权服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园授权服务中心</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江衢州市柯城区城站西路服务中心</t>
+          <t>小米汽车山西大同市云岗区庞大汽贸园服务中心</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -17983,17 +17983,17 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路授权服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路授权服务中心</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>小米汽车德阳市八角开发区金沙西路服务中心</t>
+          <t>小米汽车江西省抚州市高新技术产业开发区东临路服务中心</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
@@ -18015,17 +18015,17 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路授权服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园授权服务中心</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华市婺城区金衢路服务中心</t>
+          <t>小米汽车新疆伊犁市城投汽车产业园服务中心</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
@@ -18047,17 +18047,17 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北授权服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道授权服务中心</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>小米汽车广东省广州市白云区广州大道北服务中心</t>
+          <t>小米汽车安徽阜阳市临泉县迎宾大道服务中心</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路授权服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路授权服务中心</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>小米汽车南充市顺庆区潆康北路服务中心</t>
+          <t>小米汽车广东省肇庆市端州区东岗路服务中心</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -18106,22 +18106,22 @@
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路授权服务中心</t>
+          <t>AITO授权用户中心•贵州电动</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽省滁州琅琊区凤阳北路服务中心</t>
+          <t>AITO授权用户中心•广西电动</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -18138,22 +18138,22 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
+          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -18163,29 +18163,29 @@
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 60%</t>
+          <t>地址相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（驰宝店）</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
+          <t>理想汽车晋中榆次授权钣喷中心（航田店）</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -18195,7 +18195,7 @@
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>地址相似度 88%</t>
+          <t>地址相似度 60%</t>
         </is>
       </c>
     </row>
@@ -18212,12 +18212,12 @@
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道授权服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街授权服务中心</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市海宁市海宁大道服务中心</t>
+          <t>小米汽车浙江省杭州临平区星发街服务中心</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -18239,17 +18239,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
+          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18271,17 +18271,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
+          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18303,17 +18303,17 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
+          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -18335,17 +18335,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城授权服务中心</t>
+          <t>小米汽车江西萍乡安源区萍乡天虹</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>小米汽车邵阳市双清区大汉汽车城服务中心</t>
+          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -18367,17 +18367,17 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路授权服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路授权服务中心</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江苏省苏州市张家港市国泰北路服务中心</t>
+          <t>小米汽车浙江台州市温岭市华盛路服务中心</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18431,17 +18431,17 @@
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路授权服务中心</t>
+          <t>小米汽车兴义市桔康路授权服务中心</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>小米汽车天津西青区卫津南路服务中心</t>
+          <t>小米汽车兴义市桔康路服务中心</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 93%</t>
+          <t>店名相似度 91%</t>
         </is>
       </c>
     </row>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西萍乡安源区萍乡天虹</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省萍乡市安源区萍乡天虹</t>
+          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 94%</t>
+          <t>店名相似度 95%</t>
         </is>
       </c>
     </row>
@@ -18495,17 +18495,17 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场授权服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路授权服务中心</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>小米汽车河北省邯郸市经济开发区时代汽车广场服务中心</t>
+          <t>小米汽车漳州市龙文区龙文北路服务中心</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
@@ -18527,17 +18527,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇授权服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路授权服务中心</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>小米汽车江西省景德镇市昌南新区洪源镇服务中心</t>
+          <t>小米汽车湖北省武汉江夏区光谷一路服务中心</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 95%</t>
+          <t>店名相似度 94%</t>
         </is>
       </c>
     </row>
@@ -18559,17 +18559,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路授权服务中心</t>
+          <t>小米汽车天津西青区卫津南路授权服务中心</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>小米汽车兴义市桔康路服务中心</t>
+          <t>小米汽车天津西青区卫津南路服务中心</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 91%</t>
+          <t>店名相似度 93%</t>
         </is>
       </c>
     </row>
